--- a/Artacho2024/Metadata/Raw_metadata/meta_clinical.xlsx
+++ b/Artacho2024/Metadata/Raw_metadata/meta_clinical.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Carles/Desktop/GvHD.manuscript/rebuttal/lo.enviado/proof/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sophiehuebler/Documents/ODSi/ODSiData/Artacho2024/Metadata/Raw_metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147D3642-8A7A-8E40-A0E2-84FF5857EDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F403083E-4B12-2B4D-A631-361B79726D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9020" yWindow="540" windowWidth="34020" windowHeight="23460" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4380" yWindow="500" windowWidth="34020" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Suppl.Table.1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -25,27 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="42">
   <si>
     <t>Patient.ID</t>
   </si>
   <si>
     <t>Age</t>
-  </si>
-  <si>
-    <t>Gender (a)</t>
-  </si>
-  <si>
-    <t>Haematological malignency (b)</t>
-  </si>
-  <si>
-    <t>Type.of.tranplant (c)</t>
-  </si>
-  <si>
-    <t>Transplant.source (d)</t>
-  </si>
-  <si>
-    <t>Myelosuppression (e)</t>
   </si>
   <si>
     <t>Parenteral.Nutrition</t>
@@ -57,22 +42,13 @@
     <t>date.of.transplant</t>
   </si>
   <si>
-    <t>sample.pre (f)</t>
-  </si>
-  <si>
     <t>sample.post</t>
-  </si>
-  <si>
-    <t>Omic.analysis.pre (g)</t>
   </si>
   <si>
     <t>Omic.analysis.post</t>
   </si>
   <si>
     <t>GVHD_grade</t>
-  </si>
-  <si>
-    <t>LGI_GVHD_grade (h)</t>
   </si>
   <si>
     <t>Skin_GVHD_grade</t>
@@ -153,25 +129,28 @@
     <t>BMA</t>
   </si>
   <si>
-    <t>(a) M=male; F=Female</t>
+    <t>sample.pre</t>
   </si>
   <si>
-    <t>(b) Acute lymphoblastic leukemia (ALL); Acute myeloblastic leukemia (AML); secondary acute leukemia (SAL); other acute leukemias (OAL); Chronic myeloid leukemia (CML); Myeloprolypherative syndromes (MPS); Myelodysplastic syndrome (MDS); combined myelodysplastic/myeloprolypherative syndrome (MDS/MPS); Hodgkin's Disease (HD); Non-Hodgkin lymphoma (NHL); Multiple Myeloma &amp; Plasma cell disorders (MM); bone marrow aplasia (BMA).</t>
+    <t>Gender</t>
   </si>
   <si>
-    <t>(c) 2 = family donor, HLA identical; 4 = family donor, haploidentical; 5 =unrelated donor, HLA compatible; 6 = unrelated donor, HLA incompatible</t>
+    <t>Haematological malignency</t>
   </si>
   <si>
-    <t>(d) 1 = bone marrow; 2 = umbilical cord; 3 = peripheral blood</t>
+    <t>Type.of.tranplant</t>
   </si>
   <si>
-    <t>(e) 0 = complete; 1 = reduced</t>
+    <t>Transplant.source</t>
   </si>
   <si>
-    <t>(f) days before and after transplant. </t>
+    <t>Myelosuppression</t>
   </si>
   <si>
-    <t>(g) type of omic analysis performed: A = amplicon sequencing of 16s rRNA gene; S  = shotgun sequencing; M = metabolomic analysis</t>
+    <t>Omic.analysis.pre</t>
+  </si>
+  <si>
+    <t>LGI_GVHD_grade</t>
   </si>
 </sst>
 </file>
@@ -237,9 +216,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -277,7 +256,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -383,7 +362,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -525,7 +504,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -555,52 +534,52 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
@@ -611,10 +590,10 @@
         <v>55.416837780000002</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -626,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J2" s="2">
         <v>41604</v>
@@ -641,10 +620,10 @@
         <v>15</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O2">
         <v>2</v>
@@ -667,10 +646,10 @@
         <v>59.058179330000002</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E3">
         <v>6</v>
@@ -682,10 +661,10 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J3" s="2">
         <v>41607</v>
@@ -697,10 +676,10 @@
         <v>12</v>
       </c>
       <c r="M3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O3">
         <v>2</v>
@@ -723,10 +702,10 @@
         <v>37.530458590000002</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -738,10 +717,10 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J4" s="2">
         <v>41612</v>
@@ -753,10 +732,10 @@
         <v>14</v>
       </c>
       <c r="M4" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N4" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O4">
         <v>1</v>
@@ -779,10 +758,10 @@
         <v>36.24093087</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E5">
         <v>6</v>
@@ -794,10 +773,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J5" s="2">
         <v>41649</v>
@@ -806,10 +785,10 @@
         <v>-1</v>
       </c>
       <c r="L5" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -832,10 +811,10 @@
         <v>55.720739219999999</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -847,10 +826,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J6" s="2">
         <v>41681</v>
@@ -862,10 +841,10 @@
         <v>17</v>
       </c>
       <c r="M6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O6">
         <v>2</v>
@@ -888,10 +867,10 @@
         <v>57.91649555</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -903,10 +882,10 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I7" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J7" s="2">
         <v>41695</v>
@@ -915,7 +894,7 @@
         <v>-6</v>
       </c>
       <c r="M7" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O7">
         <v>2</v>
@@ -938,10 +917,10 @@
         <v>64.837782340000004</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E8">
         <v>6</v>
@@ -953,10 +932,10 @@
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I8" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J8" s="2">
         <v>41698</v>
@@ -968,10 +947,10 @@
         <v>12</v>
       </c>
       <c r="M8" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N8" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O8">
         <v>2</v>
@@ -994,10 +973,10 @@
         <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -1009,10 +988,10 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I9" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J9" s="2">
         <v>41709</v>
@@ -1021,7 +1000,7 @@
         <v>-5</v>
       </c>
       <c r="M9" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O9">
         <v>3</v>
@@ -1044,10 +1023,10 @@
         <v>44.881587949999997</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -1059,10 +1038,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J10" s="2">
         <v>41736</v>
@@ -1074,10 +1053,10 @@
         <v>16</v>
       </c>
       <c r="M10" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N10" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O10">
         <v>2</v>
@@ -1100,10 +1079,10 @@
         <v>56.933607119999998</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1115,10 +1094,10 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I11" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J11" s="2">
         <v>41744</v>
@@ -1127,7 +1106,7 @@
         <v>-5</v>
       </c>
       <c r="M11" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -1150,10 +1129,10 @@
         <v>45.273100620000001</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1165,10 +1144,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I12" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J12" s="2">
         <v>41752</v>
@@ -1180,10 +1159,10 @@
         <v>14</v>
       </c>
       <c r="M12" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N12" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -1206,10 +1185,10 @@
         <v>57.262149209999997</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E13">
         <v>6</v>
@@ -1221,10 +1200,10 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I13" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J13" s="2">
         <v>41753</v>
@@ -1236,10 +1215,10 @@
         <v>13</v>
       </c>
       <c r="M13" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N13" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -1262,10 +1241,10 @@
         <v>54.03969884</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -1277,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I14" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J14" s="2">
         <v>41828</v>
@@ -1289,7 +1268,7 @@
         <v>-6</v>
       </c>
       <c r="M14" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1312,10 +1291,10 @@
         <v>62.989733059999999</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -1327,10 +1306,10 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I15" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J15" s="2">
         <v>41898</v>
@@ -1339,7 +1318,7 @@
         <v>-6</v>
       </c>
       <c r="M15" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O15">
         <v>3</v>
@@ -1362,10 +1341,10 @@
         <v>18.258726899999999</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -1377,10 +1356,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I16" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J16" s="2">
         <v>41905</v>
@@ -1392,10 +1371,10 @@
         <v>17</v>
       </c>
       <c r="M16" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N16" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -1418,10 +1397,10 @@
         <v>40.591375769999999</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E17">
         <v>6</v>
@@ -1433,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I17" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J17" s="2">
         <v>41905</v>
@@ -1445,7 +1424,7 @@
         <v>-6</v>
       </c>
       <c r="M17" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O17">
         <v>2</v>
@@ -1468,10 +1447,10 @@
         <v>45.182751539999998</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E18">
         <v>6</v>
@@ -1483,10 +1462,10 @@
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I18" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J18" s="2">
         <v>41933</v>
@@ -1498,10 +1477,10 @@
         <v>16</v>
       </c>
       <c r="M18" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N18" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O18">
         <v>1</v>
@@ -1524,10 +1503,10 @@
         <v>60.659822040000002</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -1539,10 +1518,10 @@
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I19" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J19" s="2">
         <v>41934</v>
@@ -1554,10 +1533,10 @@
         <v>14</v>
       </c>
       <c r="M19" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N19" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -1580,10 +1559,10 @@
         <v>48.807665980000003</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E20">
         <v>6</v>
@@ -1595,10 +1574,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I20" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J20" s="2">
         <v>41935</v>
@@ -1607,10 +1586,10 @@
         <v>-1</v>
       </c>
       <c r="L20" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M20" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O20">
         <v>1</v>
@@ -1633,10 +1612,10 @@
         <v>44.246406569999998</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E21">
         <v>6</v>
@@ -1648,10 +1627,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I21" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J21" s="2">
         <v>42016</v>
@@ -1660,7 +1639,7 @@
         <v>-4</v>
       </c>
       <c r="M21" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -1683,10 +1662,10 @@
         <v>24.47091034</v>
       </c>
       <c r="C22" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E22">
         <v>2</v>
@@ -1698,10 +1677,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I22" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J22" s="2">
         <v>42024</v>
@@ -1710,7 +1689,7 @@
         <v>-6</v>
       </c>
       <c r="M22" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O22">
         <v>2</v>
@@ -1733,10 +1712,10 @@
         <v>31.468856949999999</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E23">
         <v>2</v>
@@ -1748,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I23" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J23" s="2">
         <v>42047</v>
@@ -1763,10 +1742,10 @@
         <v>14</v>
       </c>
       <c r="M23" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N23" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O23">
         <v>1</v>
@@ -1789,10 +1768,10 @@
         <v>18.792607799999999</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E24">
         <v>6</v>
@@ -1804,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I24" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J24" s="2">
         <v>42055</v>
@@ -1816,10 +1795,10 @@
         <v>-2</v>
       </c>
       <c r="L24" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M24" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O24">
         <v>1</v>
@@ -1842,10 +1821,10 @@
         <v>38.056125940000001</v>
       </c>
       <c r="C25" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -1857,10 +1836,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I25" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J25" s="2">
         <v>42089</v>
@@ -1872,10 +1851,10 @@
         <v>13</v>
       </c>
       <c r="M25" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N25" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -1898,10 +1877,10 @@
         <v>48.136892539999998</v>
       </c>
       <c r="C26" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E26">
         <v>2</v>
@@ -1913,10 +1892,10 @@
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I26" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J26" s="2">
         <v>42115</v>
@@ -1925,7 +1904,7 @@
         <v>-6</v>
       </c>
       <c r="M26" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O26">
         <v>4</v>
@@ -1948,10 +1927,10 @@
         <v>38.097193699999998</v>
       </c>
       <c r="C27" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E27">
         <v>4</v>
@@ -1963,10 +1942,10 @@
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I27" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J27" s="2">
         <v>42548</v>
@@ -1978,10 +1957,10 @@
         <v>14</v>
       </c>
       <c r="M27" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N27" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="O27">
         <v>2</v>
@@ -2004,25 +1983,25 @@
         <v>44.772073919999997</v>
       </c>
       <c r="C28" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>3</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28" t="s">
         <v>19</v>
       </c>
-      <c r="E28">
-        <v>2</v>
-      </c>
-      <c r="F28">
-        <v>3</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28" t="s">
-        <v>27</v>
-      </c>
       <c r="I28" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J28" s="2">
         <v>42555</v>
@@ -2034,10 +2013,10 @@
         <v>14</v>
       </c>
       <c r="M28" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N28" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -2060,10 +2039,10 @@
         <v>39.753593430000002</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E29">
         <v>2</v>
@@ -2075,10 +2054,10 @@
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J29" s="2">
         <v>42556</v>
@@ -2087,7 +2066,7 @@
         <v>-12</v>
       </c>
       <c r="M29" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O29">
         <v>2</v>
@@ -2110,10 +2089,10 @@
         <v>37.152635179999997</v>
       </c>
       <c r="C30" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E30">
         <v>2</v>
@@ -2125,10 +2104,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I30" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J30" s="2">
         <v>42562</v>
@@ -2137,7 +2116,7 @@
         <v>-6</v>
       </c>
       <c r="M30" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O30">
         <v>2</v>
@@ -2160,10 +2139,10 @@
         <v>31.624914440000001</v>
       </c>
       <c r="C31" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E31">
         <v>2</v>
@@ -2175,10 +2154,10 @@
         <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I31" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J31" s="2">
         <v>42562</v>
@@ -2187,7 +2166,7 @@
         <v>-10</v>
       </c>
       <c r="M31" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -2210,10 +2189,10 @@
         <v>54.362765230000001</v>
       </c>
       <c r="C32" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D32" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E32">
         <v>2</v>
@@ -2225,10 +2204,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I32" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J32" s="2">
         <v>42563</v>
@@ -2240,10 +2219,10 @@
         <v>14</v>
       </c>
       <c r="M32" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N32" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -2266,10 +2245,10 @@
         <v>54.674880219999999</v>
       </c>
       <c r="C33" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D33" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E33">
         <v>2</v>
@@ -2281,10 +2260,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I33" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J33" s="2">
         <v>42565</v>
@@ -2296,10 +2275,10 @@
         <v>13</v>
       </c>
       <c r="M33" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N33" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O33">
         <v>4</v>
@@ -2322,10 +2301,10 @@
         <v>45.28678987</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D34" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E34">
         <v>2</v>
@@ -2337,10 +2316,10 @@
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I34" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J34" s="2">
         <v>42573</v>
@@ -2349,7 +2328,7 @@
         <v>-3</v>
       </c>
       <c r="M34" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -2372,10 +2351,10 @@
         <v>23.797399039999998</v>
       </c>
       <c r="C35" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E35">
         <v>5</v>
@@ -2387,10 +2366,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I35" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J35" s="2">
         <v>42600</v>
@@ -2402,10 +2381,10 @@
         <v>12</v>
       </c>
       <c r="M35" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N35" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -2428,10 +2407,10 @@
         <v>21.06776181</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E36">
         <v>2</v>
@@ -2443,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I36" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J36" s="2">
         <v>42601</v>
@@ -2455,7 +2434,7 @@
         <v>-2</v>
       </c>
       <c r="M36" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -2478,10 +2457,10 @@
         <v>36.917180010000003</v>
       </c>
       <c r="C37" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D37" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E37">
         <v>2</v>
@@ -2493,10 +2472,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I37" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J37" s="2">
         <v>42607</v>
@@ -2508,10 +2487,10 @@
         <v>15</v>
       </c>
       <c r="M37" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N37" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -2534,10 +2513,10 @@
         <v>58.73511294</v>
       </c>
       <c r="C38" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D38" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -2549,10 +2528,10 @@
         <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I38" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J38" s="2">
         <v>42632</v>
@@ -2561,7 +2540,7 @@
         <v>-6</v>
       </c>
       <c r="M38" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -2584,10 +2563,10 @@
         <v>58.628336760000003</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D39" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E39">
         <v>5</v>
@@ -2599,10 +2578,10 @@
         <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I39" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J39" s="2">
         <v>42650</v>
@@ -2611,7 +2590,7 @@
         <v>-4</v>
       </c>
       <c r="M39" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O39">
         <v>3</v>
@@ -2634,10 +2613,10 @@
         <v>54.548939079999997</v>
       </c>
       <c r="C40" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D40" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E40">
         <v>5</v>
@@ -2649,10 +2628,10 @@
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I40" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J40" s="2">
         <v>42656</v>
@@ -2664,10 +2643,10 @@
         <v>12</v>
       </c>
       <c r="M40" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N40" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -2690,10 +2669,10 @@
         <v>39.397672829999998</v>
       </c>
       <c r="C41" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E41">
         <v>5</v>
@@ -2705,10 +2684,10 @@
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I41" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J41" s="2">
         <v>42656</v>
@@ -2720,10 +2699,10 @@
         <v>14</v>
       </c>
       <c r="M41" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N41" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -2746,10 +2725,10 @@
         <v>42.872005479999999</v>
       </c>
       <c r="C42" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D42" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E42">
         <v>5</v>
@@ -2761,10 +2740,10 @@
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I42" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J42" s="2">
         <v>42663</v>
@@ -2773,7 +2752,7 @@
         <v>-2</v>
       </c>
       <c r="M42" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O42">
         <v>2</v>
@@ -2796,10 +2775,10 @@
         <v>70.480492810000001</v>
       </c>
       <c r="C43" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D43" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E43">
         <v>2</v>
@@ -2811,10 +2790,10 @@
         <v>1</v>
       </c>
       <c r="H43" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I43" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J43" s="2">
         <v>42669</v>
@@ -2826,10 +2805,10 @@
         <v>13</v>
       </c>
       <c r="M43" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N43" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O43">
         <v>1</v>
@@ -2852,10 +2831,10 @@
         <v>37.062286110000002</v>
       </c>
       <c r="C44" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D44" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E44">
         <v>6</v>
@@ -2867,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I44" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J44" s="2">
         <v>42669</v>
@@ -2879,7 +2858,7 @@
         <v>-6</v>
       </c>
       <c r="M44" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -2902,10 +2881,10 @@
         <v>59.786447639999999</v>
       </c>
       <c r="C45" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D45" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E45">
         <v>2</v>
@@ -2917,10 +2896,10 @@
         <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I45" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J45" s="2">
         <v>42683</v>
@@ -2932,10 +2911,10 @@
         <v>13</v>
       </c>
       <c r="M45" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N45" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O45">
         <v>3</v>
@@ -2958,10 +2937,10 @@
         <v>53.451060920000003</v>
       </c>
       <c r="C46" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E46">
         <v>6</v>
@@ -2973,10 +2952,10 @@
         <v>1</v>
       </c>
       <c r="H46" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I46" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J46" s="2">
         <v>42684</v>
@@ -2988,10 +2967,10 @@
         <v>14</v>
       </c>
       <c r="M46" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N46" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -3014,10 +2993,10 @@
         <v>27.887748120000001</v>
       </c>
       <c r="C47" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D47" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E47">
         <v>6</v>
@@ -3029,10 +3008,10 @@
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I47" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J47" s="2">
         <v>42685</v>
@@ -3044,10 +3023,10 @@
         <v>14</v>
       </c>
       <c r="M47" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N47" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O47">
         <v>1</v>
@@ -3070,10 +3049,10 @@
         <v>52.238193019999997</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D48" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E48">
         <v>4</v>
@@ -3085,10 +3064,10 @@
         <v>1</v>
       </c>
       <c r="H48" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I48" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J48" s="2">
         <v>42689</v>
@@ -3097,7 +3076,7 @@
         <v>-5</v>
       </c>
       <c r="M48" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O48">
         <v>2</v>
@@ -3120,10 +3099,10 @@
         <v>40.91444216</v>
       </c>
       <c r="C49" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D49" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E49">
         <v>4</v>
@@ -3135,10 +3114,10 @@
         <v>1</v>
       </c>
       <c r="H49" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I49" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J49" s="2">
         <v>42696</v>
@@ -3150,10 +3129,10 @@
         <v>15</v>
       </c>
       <c r="M49" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="N49" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O49">
         <v>2</v>
@@ -3176,10 +3155,10 @@
         <v>59.605749490000001</v>
       </c>
       <c r="C50" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E50">
         <v>2</v>
@@ -3191,10 +3170,10 @@
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I50" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J50" s="2">
         <v>42696</v>
@@ -3206,10 +3185,10 @@
         <v>15</v>
       </c>
       <c r="M50" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N50" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="O50">
         <v>2</v>
@@ -3232,10 +3211,10 @@
         <v>52.501026690000003</v>
       </c>
       <c r="C51" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D51" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E51">
         <v>5</v>
@@ -3247,10 +3226,10 @@
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I51" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J51" s="2">
         <v>42712</v>
@@ -3262,10 +3241,10 @@
         <v>12</v>
       </c>
       <c r="M51" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N51" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O51">
         <v>2</v>
@@ -3288,25 +3267,25 @@
         <v>41.297741270000003</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D52" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52">
+        <v>3</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52" t="s">
         <v>19</v>
       </c>
-      <c r="E52">
-        <v>2</v>
-      </c>
-      <c r="F52">
-        <v>3</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52" t="s">
-        <v>27</v>
-      </c>
       <c r="I52" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J52" s="2">
         <v>42716</v>
@@ -3315,10 +3294,10 @@
         <v>0</v>
       </c>
       <c r="L52" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M52" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O52">
         <v>2</v>
@@ -3341,10 +3320,10 @@
         <v>52.922655720000002</v>
       </c>
       <c r="C53" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E53">
         <v>6</v>
@@ -3356,10 +3335,10 @@
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I53" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J53" s="2">
         <v>42726</v>
@@ -3368,7 +3347,7 @@
         <v>-6</v>
       </c>
       <c r="M53" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -3391,10 +3370,10 @@
         <v>61.185489390000001</v>
       </c>
       <c r="C54" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D54" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E54">
         <v>6</v>
@@ -3406,10 +3385,10 @@
         <v>1</v>
       </c>
       <c r="H54" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I54" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J54" s="2">
         <v>42734</v>
@@ -3421,10 +3400,10 @@
         <v>13</v>
       </c>
       <c r="M54" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N54" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O54">
         <v>3</v>
@@ -3447,10 +3426,10 @@
         <v>51.89048597</v>
       </c>
       <c r="C55" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E55">
         <v>5</v>
@@ -3462,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I55" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J55" s="2">
         <v>42734</v>
@@ -3477,10 +3456,10 @@
         <v>13</v>
       </c>
       <c r="M55" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N55" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="O55">
         <v>1</v>
@@ -3503,25 +3482,25 @@
         <v>42.357289530000003</v>
       </c>
       <c r="C56" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D56" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56">
+        <v>2</v>
+      </c>
+      <c r="F56">
+        <v>3</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56" t="s">
         <v>19</v>
       </c>
-      <c r="E56">
-        <v>2</v>
-      </c>
-      <c r="F56">
-        <v>3</v>
-      </c>
-      <c r="G56">
-        <v>0</v>
-      </c>
-      <c r="H56" t="s">
-        <v>27</v>
-      </c>
       <c r="I56" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J56" s="2">
         <v>42738</v>
@@ -3533,10 +3512,10 @@
         <v>14</v>
       </c>
       <c r="M56" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N56" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -3559,10 +3538,10 @@
         <v>34.855578370000003</v>
       </c>
       <c r="C57" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E57">
         <v>6</v>
@@ -3574,10 +3553,10 @@
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I57" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J57" s="2">
         <v>42751</v>
@@ -3589,10 +3568,10 @@
         <v>15</v>
       </c>
       <c r="M57" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N57" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O57">
         <v>2</v>
@@ -3615,10 +3594,10 @@
         <v>36.350444899999999</v>
       </c>
       <c r="C58" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D58" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E58">
         <v>5</v>
@@ -3630,10 +3609,10 @@
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I58" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J58" s="2">
         <v>42759</v>
@@ -3645,10 +3624,10 @@
         <v>15</v>
       </c>
       <c r="M58" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N58" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="O58">
         <v>0</v>
@@ -3671,10 +3650,10 @@
         <v>59</v>
       </c>
       <c r="C59" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D59" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -3686,10 +3665,10 @@
         <v>1</v>
       </c>
       <c r="H59" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I59" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J59" s="2">
         <v>42767</v>
@@ -3701,10 +3680,10 @@
         <v>11</v>
       </c>
       <c r="M59" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N59" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -3727,10 +3706,10 @@
         <v>62.308008209999997</v>
       </c>
       <c r="C60" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E60">
         <v>2</v>
@@ -3742,10 +3721,10 @@
         <v>1</v>
       </c>
       <c r="H60" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I60" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J60" s="2">
         <v>42787</v>
@@ -3757,10 +3736,10 @@
         <v>14</v>
       </c>
       <c r="M60" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N60" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -3783,10 +3762,10 @@
         <v>32.470910340000003</v>
       </c>
       <c r="C61" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" t="s">
         <v>22</v>
-      </c>
-      <c r="D61" t="s">
-        <v>30</v>
       </c>
       <c r="E61">
         <v>6</v>
@@ -3798,10 +3777,10 @@
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I61" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J61" s="2">
         <v>42789</v>
@@ -3813,10 +3792,10 @@
         <v>14</v>
       </c>
       <c r="M61" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N61" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O61">
         <v>2</v>
@@ -3839,10 +3818,10 @@
         <v>41.007529089999998</v>
       </c>
       <c r="C62" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D62" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E62">
         <v>5</v>
@@ -3854,10 +3833,10 @@
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I62" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J62" s="2">
         <v>42790</v>
@@ -3869,10 +3848,10 @@
         <v>14</v>
       </c>
       <c r="M62" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N62" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="O62">
         <v>2</v>
@@ -3895,10 +3874,10 @@
         <v>21.790554409999999</v>
       </c>
       <c r="C63" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D63" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E63">
         <v>6</v>
@@ -3910,10 +3889,10 @@
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I63" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J63" s="2">
         <v>42793</v>
@@ -3925,10 +3904,10 @@
         <v>14</v>
       </c>
       <c r="M63" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N63" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -3951,10 +3930,10 @@
         <v>44.049281309999998</v>
       </c>
       <c r="C64" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D64" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E64">
         <v>2</v>
@@ -3966,10 +3945,10 @@
         <v>1</v>
       </c>
       <c r="H64" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I64" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J64" s="2">
         <v>42797</v>
@@ -3978,7 +3957,7 @@
         <v>-2</v>
       </c>
       <c r="M64" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -4001,10 +3980,10 @@
         <v>64.947296370000004</v>
       </c>
       <c r="C65" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E65">
         <v>4</v>
@@ -4016,10 +3995,10 @@
         <v>1</v>
       </c>
       <c r="H65" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I65" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J65" s="2">
         <v>42802</v>
@@ -4031,10 +4010,10 @@
         <v>14</v>
       </c>
       <c r="M65" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N65" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="O65">
         <v>2</v>
@@ -4057,10 +4036,10 @@
         <v>22.781656399999999</v>
       </c>
       <c r="C66" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D66" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E66">
         <v>4</v>
@@ -4072,10 +4051,10 @@
         <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I66" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J66" s="2">
         <v>42809</v>
@@ -4087,10 +4066,10 @@
         <v>14</v>
       </c>
       <c r="M66" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N66" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O66">
         <v>4</v>
@@ -4113,10 +4092,10 @@
         <v>32.583162219999998</v>
       </c>
       <c r="C67" t="s">
+        <v>14</v>
+      </c>
+      <c r="D67" t="s">
         <v>22</v>
-      </c>
-      <c r="D67" t="s">
-        <v>30</v>
       </c>
       <c r="E67">
         <v>5</v>
@@ -4128,10 +4107,10 @@
         <v>0</v>
       </c>
       <c r="H67" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I67" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J67" s="2">
         <v>42814</v>
@@ -4143,10 +4122,10 @@
         <v>16</v>
       </c>
       <c r="M67" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N67" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O67">
         <v>0</v>
@@ -4169,10 +4148,10 @@
         <v>60.413415469999997</v>
       </c>
       <c r="C68" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E68">
         <v>4</v>
@@ -4184,10 +4163,10 @@
         <v>1</v>
       </c>
       <c r="H68" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I68" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J68" s="2">
         <v>42816</v>
@@ -4199,10 +4178,10 @@
         <v>14</v>
       </c>
       <c r="M68" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N68" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -4225,10 +4204,10 @@
         <v>45.505817929999999</v>
       </c>
       <c r="C69" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E69">
         <v>4</v>
@@ -4240,10 +4219,10 @@
         <v>1</v>
       </c>
       <c r="H69" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I69" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J69" s="2">
         <v>42821</v>
@@ -4255,10 +4234,10 @@
         <v>14</v>
       </c>
       <c r="M69" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N69" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O69">
         <v>3</v>
@@ -4281,10 +4260,10 @@
         <v>57.530458590000002</v>
       </c>
       <c r="C70" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D70" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E70">
         <v>2</v>
@@ -4296,10 +4275,10 @@
         <v>1</v>
       </c>
       <c r="H70" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I70" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J70" s="2">
         <v>42822</v>
@@ -4311,10 +4290,10 @@
         <v>14</v>
       </c>
       <c r="M70" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N70" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O70">
         <v>0</v>
@@ -4337,10 +4316,10 @@
         <v>45.585215609999999</v>
       </c>
       <c r="C71" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D71" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E71">
         <v>2</v>
@@ -4352,10 +4331,10 @@
         <v>0</v>
       </c>
       <c r="H71" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I71" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J71" s="2">
         <v>42823</v>
@@ -4367,10 +4346,10 @@
         <v>13</v>
       </c>
       <c r="M71" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N71" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4393,10 +4372,10 @@
         <v>56.344969200000001</v>
       </c>
       <c r="C72" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D72" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E72">
         <v>4</v>
@@ -4408,10 +4387,10 @@
         <v>0</v>
       </c>
       <c r="H72" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I72" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J72" s="2">
         <v>42829</v>
@@ -4423,10 +4402,10 @@
         <v>14</v>
       </c>
       <c r="M72" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N72" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4449,10 +4428,10 @@
         <v>43.572895279999997</v>
       </c>
       <c r="C73" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D73" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E73">
         <v>6</v>
@@ -4464,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="H73" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I73" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J73" s="2">
         <v>42852</v>
@@ -4479,10 +4458,10 @@
         <v>14</v>
       </c>
       <c r="M73" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N73" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O73">
         <v>2</v>
@@ -4505,10 +4484,10 @@
         <v>37.240246409999997</v>
       </c>
       <c r="C74" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E74">
         <v>2</v>
@@ -4520,10 +4499,10 @@
         <v>0</v>
       </c>
       <c r="H74" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I74" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J74" s="2">
         <v>42858</v>
@@ -4532,7 +4511,7 @@
         <v>-1</v>
       </c>
       <c r="M74" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -4555,10 +4534,10 @@
         <v>53.620807669999998</v>
       </c>
       <c r="C75" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E75">
         <v>5</v>
@@ -4570,10 +4549,10 @@
         <v>0</v>
       </c>
       <c r="H75" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I75" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J75" s="2">
         <v>42860</v>
@@ -4585,10 +4564,10 @@
         <v>14</v>
       </c>
       <c r="M75" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N75" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O75">
         <v>2</v>
@@ -4611,10 +4590,10 @@
         <v>20.451745379999998</v>
       </c>
       <c r="C76" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D76" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E76">
         <v>6</v>
@@ -4626,10 +4605,10 @@
         <v>0</v>
       </c>
       <c r="H76" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I76" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J76" s="2">
         <v>42866</v>
@@ -4638,7 +4617,7 @@
         <v>-3</v>
       </c>
       <c r="M76" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O76">
         <v>4</v>
@@ -4661,10 +4640,10 @@
         <v>54.428473650000001</v>
       </c>
       <c r="C77" t="s">
+        <v>14</v>
+      </c>
+      <c r="D77" t="s">
         <v>22</v>
-      </c>
-      <c r="D77" t="s">
-        <v>30</v>
       </c>
       <c r="E77">
         <v>6</v>
@@ -4676,10 +4655,10 @@
         <v>0</v>
       </c>
       <c r="H77" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I77" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J77" s="2">
         <v>42881</v>
@@ -4691,10 +4670,10 @@
         <v>14</v>
       </c>
       <c r="M77" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N77" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O77">
         <v>2</v>
@@ -4717,10 +4696,10 @@
         <v>51.534565370000003</v>
       </c>
       <c r="C78" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E78">
         <v>4</v>
@@ -4732,10 +4711,10 @@
         <v>1</v>
       </c>
       <c r="H78" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I78" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J78" s="2">
         <v>42887</v>
@@ -4747,10 +4726,10 @@
         <v>14</v>
       </c>
       <c r="M78" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N78" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="O78">
         <v>2</v>
@@ -4773,10 +4752,10 @@
         <v>43.994524300000002</v>
       </c>
       <c r="C79" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E79">
         <v>5</v>
@@ -4788,10 +4767,10 @@
         <v>0</v>
       </c>
       <c r="H79" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I79" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J79" s="2">
         <v>42887</v>
@@ -4803,10 +4782,10 @@
         <v>14</v>
       </c>
       <c r="M79" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N79" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -4829,10 +4808,10 @@
         <v>37.355236140000002</v>
       </c>
       <c r="C80" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E80">
         <v>4</v>
@@ -4844,10 +4823,10 @@
         <v>0</v>
       </c>
       <c r="H80" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I80" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J80" s="2">
         <v>42894</v>
@@ -4859,10 +4838,10 @@
         <v>14</v>
       </c>
       <c r="M80" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N80" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -4885,10 +4864,10 @@
         <v>52.813141680000001</v>
       </c>
       <c r="C81" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D81" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E81">
         <v>4</v>
@@ -4900,10 +4879,10 @@
         <v>0</v>
       </c>
       <c r="H81" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I81" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J81" s="2">
         <v>42898</v>
@@ -4915,10 +4894,10 @@
         <v>14</v>
       </c>
       <c r="M81" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N81" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -4941,10 +4920,10 @@
         <v>49</v>
       </c>
       <c r="C82" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D82" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -4956,10 +4935,10 @@
         <v>1</v>
       </c>
       <c r="H82" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I82" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J82" s="2">
         <v>42900</v>
@@ -4971,10 +4950,10 @@
         <v>13</v>
       </c>
       <c r="M82" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N82" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -4997,10 +4976,10 @@
         <v>41.943874059999999</v>
       </c>
       <c r="C83" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D83" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E83">
         <v>5</v>
@@ -5012,10 +4991,10 @@
         <v>0</v>
       </c>
       <c r="H83" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I83" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J83" s="2">
         <v>42905</v>
@@ -5027,10 +5006,10 @@
         <v>14</v>
       </c>
       <c r="M83" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="N83" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O83">
         <v>0</v>
@@ -5053,10 +5032,10 @@
         <v>61.957563309999998</v>
       </c>
       <c r="C84" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D84" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E84">
         <v>5</v>
@@ -5068,10 +5047,10 @@
         <v>1</v>
       </c>
       <c r="H84" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I84" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J84" s="2">
         <v>42905</v>
@@ -5083,10 +5062,10 @@
         <v>14</v>
       </c>
       <c r="M84" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N84" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -5109,10 +5088,10 @@
         <v>37.596167010000002</v>
       </c>
       <c r="C85" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E85">
         <v>6</v>
@@ -5124,10 +5103,10 @@
         <v>0</v>
       </c>
       <c r="H85" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I85" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J85" s="2">
         <v>42912</v>
@@ -5139,10 +5118,10 @@
         <v>17</v>
       </c>
       <c r="M85" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N85" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="O85">
         <v>2</v>
@@ -5165,11 +5144,11 @@
         <v>63.663244349999999</v>
       </c>
       <c r="C86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" t="s">
         <v>22</v>
       </c>
-      <c r="D86" t="s">
-        <v>30</v>
-      </c>
       <c r="E86">
         <v>2</v>
       </c>
@@ -5180,10 +5159,10 @@
         <v>1</v>
       </c>
       <c r="H86" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I86" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J86" s="2">
         <v>42914</v>
@@ -5192,7 +5171,7 @@
         <v>-2</v>
       </c>
       <c r="M86" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O86">
         <v>2</v>
@@ -5215,10 +5194,10 @@
         <v>24.96919918</v>
       </c>
       <c r="C87" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E87">
         <v>6</v>
@@ -5230,10 +5209,10 @@
         <v>0</v>
       </c>
       <c r="H87" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I87" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J87" s="2">
         <v>42921</v>
@@ -5245,10 +5224,10 @@
         <v>16</v>
       </c>
       <c r="M87" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N87" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -5271,10 +5250,10 @@
         <v>44.919917859999998</v>
       </c>
       <c r="C88" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E88">
         <v>4</v>
@@ -5286,10 +5265,10 @@
         <v>1</v>
       </c>
       <c r="H88" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I88" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J88" s="2">
         <v>42929</v>
@@ -5298,7 +5277,7 @@
         <v>-6</v>
       </c>
       <c r="M88" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O88">
         <v>3</v>
@@ -5321,10 +5300,10 @@
         <v>28.104038330000002</v>
       </c>
       <c r="C89" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D89" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E89">
         <v>4</v>
@@ -5336,10 +5315,10 @@
         <v>0</v>
       </c>
       <c r="H89" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I89" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J89" s="2">
         <v>42936</v>
@@ -5351,10 +5330,10 @@
         <v>15</v>
       </c>
       <c r="M89" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N89" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O89">
         <v>3</v>
@@ -5377,10 +5356,10 @@
         <v>27.72621492</v>
       </c>
       <c r="C90" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D90" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E90">
         <v>5</v>
@@ -5392,10 +5371,10 @@
         <v>0</v>
       </c>
       <c r="H90" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I90" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J90" s="2">
         <v>42936</v>
@@ -5404,10 +5383,10 @@
         <v>-1</v>
       </c>
       <c r="L90" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M90" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O90">
         <v>0</v>
@@ -5430,10 +5409,10 @@
         <v>26.707734429999999</v>
       </c>
       <c r="C91" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E91">
         <v>6</v>
@@ -5445,10 +5424,10 @@
         <v>0</v>
       </c>
       <c r="H91" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I91" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J91" s="2">
         <v>42948</v>
@@ -5460,10 +5439,10 @@
         <v>15</v>
       </c>
       <c r="M91" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="N91" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O91">
         <v>4</v>
@@ -5486,10 +5465,10 @@
         <v>62.431211500000003</v>
       </c>
       <c r="C92" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E92">
         <v>4</v>
@@ -5501,10 +5480,10 @@
         <v>1</v>
       </c>
       <c r="H92" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I92" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J92" s="2">
         <v>42970</v>
@@ -5516,10 +5495,10 @@
         <v>14</v>
       </c>
       <c r="M92" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N92" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O92">
         <v>2</v>
@@ -5542,10 +5521,10 @@
         <v>49.998631070000002</v>
       </c>
       <c r="C93" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D93" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E93">
         <v>2</v>
@@ -5557,10 +5536,10 @@
         <v>0</v>
       </c>
       <c r="H93" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I93" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J93" s="2">
         <v>42971</v>
@@ -5572,10 +5551,10 @@
         <v>14</v>
       </c>
       <c r="M93" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="N93" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="O93">
         <v>3</v>
@@ -5598,10 +5577,10 @@
         <v>62.784394249999998</v>
       </c>
       <c r="C94" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D94" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E94">
         <v>2</v>
@@ -5613,10 +5592,10 @@
         <v>1</v>
       </c>
       <c r="H94" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I94" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J94" s="2">
         <v>42983</v>
@@ -5628,10 +5607,10 @@
         <v>14</v>
       </c>
       <c r="M94" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N94" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -5654,10 +5633,10 @@
         <v>57.152635179999997</v>
       </c>
       <c r="C95" t="s">
+        <v>10</v>
+      </c>
+      <c r="D95" t="s">
         <v>18</v>
-      </c>
-      <c r="D95" t="s">
-        <v>26</v>
       </c>
       <c r="E95">
         <v>4</v>
@@ -5669,10 +5648,10 @@
         <v>1</v>
       </c>
       <c r="H95" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I95" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J95" s="2">
         <v>42985</v>
@@ -5684,10 +5663,10 @@
         <v>14</v>
       </c>
       <c r="M95" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N95" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="O95">
         <v>0</v>
@@ -5710,10 +5689,10 @@
         <v>69.601642709999993</v>
       </c>
       <c r="C96" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D96" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E96">
         <v>4</v>
@@ -5725,10 +5704,10 @@
         <v>1</v>
       </c>
       <c r="H96" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I96" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J96" s="2">
         <v>42985</v>
@@ -5740,10 +5719,10 @@
         <v>14</v>
       </c>
       <c r="M96" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N96" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="O96">
         <v>4</v>
@@ -5766,10 +5745,10 @@
         <v>65.500342230000001</v>
       </c>
       <c r="C97" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D97" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E97">
         <v>2</v>
@@ -5781,10 +5760,10 @@
         <v>1</v>
       </c>
       <c r="H97" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I97" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J97" s="2">
         <v>43006</v>
@@ -5796,10 +5775,10 @@
         <v>13</v>
       </c>
       <c r="M97" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N97" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O97">
         <v>2</v>
@@ -5822,10 +5801,10 @@
         <v>38.882956880000002</v>
       </c>
       <c r="C98" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D98" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E98">
         <v>5</v>
@@ -5837,10 +5816,10 @@
         <v>0</v>
       </c>
       <c r="H98" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I98" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J98" s="2">
         <v>43018</v>
@@ -5849,7 +5828,7 @@
         <v>-6</v>
       </c>
       <c r="M98" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="O98">
         <v>1</v>
@@ -5872,10 +5851,10 @@
         <v>57.084188910000002</v>
       </c>
       <c r="C99" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D99" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -5887,10 +5866,10 @@
         <v>1</v>
       </c>
       <c r="H99" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I99" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J99" s="2">
         <v>43031</v>
@@ -5902,10 +5881,10 @@
         <v>11</v>
       </c>
       <c r="M99" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N99" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O99">
         <v>3</v>
@@ -5928,10 +5907,10 @@
         <v>59.069130729999998</v>
       </c>
       <c r="C100" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D100" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E100">
         <v>5</v>
@@ -5943,10 +5922,10 @@
         <v>1</v>
       </c>
       <c r="H100" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I100" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J100" s="2">
         <v>43049</v>
@@ -5958,10 +5937,10 @@
         <v>14</v>
       </c>
       <c r="M100" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N100" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="O100">
         <v>1</v>
@@ -5984,10 +5963,10 @@
         <v>45.68925394</v>
       </c>
       <c r="C101" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D101" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -5999,10 +5978,10 @@
         <v>0</v>
       </c>
       <c r="H101" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I101" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J101" s="2">
         <v>43052</v>
@@ -6014,10 +5993,10 @@
         <v>14</v>
       </c>
       <c r="M101" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="N101" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O101">
         <v>0</v>
@@ -6040,10 +6019,10 @@
         <v>29.325119780000001</v>
       </c>
       <c r="C102" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D102" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E102">
         <v>4</v>
@@ -6055,10 +6034,10 @@
         <v>1</v>
       </c>
       <c r="H102" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I102" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J102" s="2">
         <v>43054</v>
@@ -6070,10 +6049,10 @@
         <v>14</v>
       </c>
       <c r="M102" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N102" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O102">
         <v>2</v>
@@ -6096,10 +6075,10 @@
         <v>21.54962355</v>
       </c>
       <c r="C103" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D103" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E103">
         <v>4</v>
@@ -6111,10 +6090,10 @@
         <v>0</v>
       </c>
       <c r="H103" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I103" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J103" s="2">
         <v>43061</v>
@@ -6123,7 +6102,7 @@
         <v>-12</v>
       </c>
       <c r="M103" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O103">
         <v>0</v>
@@ -6146,10 +6125,10 @@
         <v>42.658453110000004</v>
       </c>
       <c r="C104" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D104" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E104">
         <v>2</v>
@@ -6161,10 +6140,10 @@
         <v>1</v>
       </c>
       <c r="H104" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I104" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J104" s="2">
         <v>43062</v>
@@ -6173,7 +6152,7 @@
         <v>-6</v>
       </c>
       <c r="M104" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O104">
         <v>0</v>
@@ -6196,25 +6175,25 @@
         <v>18.444900749999999</v>
       </c>
       <c r="C105" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D105" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105">
+        <v>2</v>
+      </c>
+      <c r="F105">
+        <v>3</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105" t="s">
         <v>19</v>
       </c>
-      <c r="E105">
-        <v>2</v>
-      </c>
-      <c r="F105">
-        <v>3</v>
-      </c>
-      <c r="G105">
-        <v>0</v>
-      </c>
-      <c r="H105" t="s">
-        <v>27</v>
-      </c>
       <c r="I105" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J105" s="2">
         <v>43066</v>
@@ -6223,10 +6202,10 @@
         <v>0</v>
       </c>
       <c r="L105" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M105" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O105">
         <v>0</v>
@@ -6249,10 +6228,10 @@
         <v>51.969883639999999</v>
       </c>
       <c r="C106" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D106" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E106">
         <v>2</v>
@@ -6264,10 +6243,10 @@
         <v>1</v>
       </c>
       <c r="H106" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I106" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J106" s="2">
         <v>43080</v>
@@ -6276,7 +6255,7 @@
         <v>-4</v>
       </c>
       <c r="M106" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O106">
         <v>2</v>
@@ -6292,39 +6271,25 @@
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A110" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="A110" s="1"/>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A111" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="A111" s="1"/>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A112" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="A112" s="1"/>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A113" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="A113" s="1"/>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A114" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="A114" s="1"/>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A115" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="A115" s="1"/>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A116" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="A116" s="1"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R106">
@@ -6337,4 +6302,10 @@
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{170051ed-867f-4092-a6af-8a42e27b7e09}" enabled="1" method="Standard" siteId="{5217e0e7-539d-4563-b1bf-7c6dcf074f91}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>